--- a/teste/Plants_teste.xlsx
+++ b/teste/Plants_teste.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ead127730922d462/DOUTORADO/0.TESE/modelagem/modelo_bru/teste/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{B62E733F-E2E4-4012-8470-C1B541D273FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EECD42C-9C6C-445A-816C-F509010FFCDA}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{B62E733F-E2E4-4012-8470-C1B541D273FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E20BE7B-8381-4996-96AD-5D180B5DBD3F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1683CF16-D6CE-428F-8B93-DD97FDAC2386}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Coordinates</t>
   </si>
@@ -65,16 +65,25 @@
     <t>Plantname</t>
   </si>
   <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
     <t>P1</t>
   </si>
   <si>
     <t>P2</t>
+  </si>
+  <si>
+    <t>Startyear</t>
+  </si>
+  <si>
+    <t>Energy_intensity</t>
+  </si>
+  <si>
+    <t>Emission_intensity</t>
+  </si>
+  <si>
+    <t>BF-BOF</t>
+  </si>
+  <si>
+    <t>EAF</t>
   </si>
 </sst>
 </file>
@@ -470,18 +479,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBFE9D97-E7E6-401A-8B63-E7AB508DAAF6}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.88671875" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -498,15 +509,24 @@
         <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -518,18 +538,27 @@
         <v>-43752950</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="4">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G2" s="4">
         <v>2036</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I2">
+        <v>23</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>4</v>
@@ -541,149 +570,173 @@
         <v>-40242298</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2033</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I3">
         <v>10</v>
       </c>
-      <c r="F3" s="4">
-        <v>2033</v>
-      </c>
-      <c r="G3" s="3">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F4" s="1"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F5" s="1"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F6" s="1"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F7" s="1"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F8" s="1"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F9" s="1"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F10" s="1"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="1"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F11" s="1"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F12" s="1"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F13" s="1"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F14" s="1"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F15" s="1"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F16" s="1"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F17" s="1"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="3"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
